--- a/preview/pr-14/CodeSystem-ede-q6-tage.xlsx
+++ b/preview/pr-14/CodeSystem-ede-q6-tage.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T09:08:36+00:00</t>
+    <t>2026-09-30T09:23:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -160,40 +160,40 @@
     <t>0</t>
   </si>
   <si>
-    <t>kein Tag</t>
-  </si>
-  <si>
-    <t>1–5 Tage</t>
+    <t>No days</t>
+  </si>
+  <si>
+    <t>1-5 days</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>6–12 Tage</t>
+    <t>6-12 days</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>13–15 Tage</t>
+    <t>13-15 days</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>16–22 Tage</t>
+    <t>16-22 days</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>23–27 Tage</t>
+    <t>23-27 days</t>
   </si>
   <si>
     <t>6</t>
   </si>
   <si>
-    <t>jeden Tag</t>
+    <t>Every day</t>
   </si>
 </sst>
 </file>

--- a/preview/pr-14/CodeSystem-ede-q6-tage.xlsx
+++ b/preview/pr-14/CodeSystem-ede-q6-tage.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T09:23:41+00:00</t>
+    <t>2026-09-30T09:31:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -85,7 +85,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>7-stufige Häufigkeitsskala der EDE-Q-Items über die letzten 28 Tage (0 = kein Tag ... 6 = jeden Tag). ordinalValue-Property je Konzept für SDC-Scoring via .ordinal().</t>
+    <t>7-stufige Häufigkeitsskala der EDE-Q-Items über die letzten 28 Tage (0 = kein Tag ... 6 = jeden Tag). ordinalValue-Property je Konzept für SDC-Scoring via .ordinal(). Jedes Item trägt in `item.code` seine PCOR-MII-Dictionary-Variable — das ist der PCOR-MII-Code des Items. Hier stimmt sie mit der Itemnummer überein.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/preview/pr-14/CodeSystem-ede-q6-tage.xlsx
+++ b/preview/pr-14/CodeSystem-ede-q6-tage.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T09:31:14+00:00</t>
+    <t>2026-09-30T09:36:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
